--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129962526</v>
+        <v>129962496</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560557</v>
+        <v>560548</v>
       </c>
       <c r="R2" t="n">
-        <v>6684881</v>
+        <v>6684894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129962496</v>
+        <v>129962526</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560548</v>
+        <v>560557</v>
       </c>
       <c r="R3" t="n">
-        <v>6684894</v>
+        <v>6684881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1470,54 +1470,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>92557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R9" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,45 +1577,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B10" t="n">
-        <v>92557</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R10" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,45 +1805,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129962501</v>
+        <v>129962503</v>
       </c>
       <c r="B12" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560587</v>
+        <v>560720</v>
       </c>
       <c r="R12" t="n">
-        <v>6684762</v>
+        <v>6684848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,50 +1917,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962503</v>
+        <v>129962501</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560720</v>
+        <v>560587</v>
       </c>
       <c r="R13" t="n">
-        <v>6684848</v>
+        <v>6684762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,38 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129962495</v>
+        <v>129962500</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>4773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560546</v>
+        <v>560603</v>
       </c>
       <c r="R14" t="n">
-        <v>6684846</v>
+        <v>6684818</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,38 +2136,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129962500</v>
+        <v>129962495</v>
       </c>
       <c r="B15" t="n">
-        <v>4773</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560603</v>
+        <v>560546</v>
       </c>
       <c r="R15" t="n">
-        <v>6684818</v>
+        <v>6684846</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,42 +2369,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962512</v>
+        <v>129962488</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2413,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560755</v>
+        <v>560605</v>
       </c>
       <c r="R17" t="n">
-        <v>6685020</v>
+        <v>6684821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,38 +2481,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129962488</v>
+        <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560605</v>
+        <v>560755</v>
       </c>
       <c r="R18" t="n">
-        <v>6684821</v>
+        <v>6685020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129962493</v>
+        <v>129962507</v>
       </c>
       <c r="B19" t="n">
-        <v>92557</v>
+        <v>58108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560790</v>
+        <v>560846</v>
       </c>
       <c r="R19" t="n">
-        <v>6685002</v>
+        <v>6685065</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129962507</v>
+        <v>129962493</v>
       </c>
       <c r="B20" t="n">
-        <v>58108</v>
+        <v>92557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560846</v>
+        <v>560790</v>
       </c>
       <c r="R20" t="n">
-        <v>6685065</v>
+        <v>6685002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,7 +2811,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129962515</v>
+        <v>129962509</v>
       </c>
       <c r="B21" t="n">
         <v>98794</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2849,16 +2849,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560563</v>
+        <v>560768</v>
       </c>
       <c r="R21" t="n">
-        <v>6684722</v>
+        <v>6685002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2900,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,7 +2932,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129962509</v>
+        <v>129962515</v>
       </c>
       <c r="B22" t="n">
         <v>98794</v>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2965,21 +2970,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560768</v>
+        <v>560563</v>
       </c>
       <c r="R22" t="n">
-        <v>6685002</v>
+        <v>6684722</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129962519</v>
+        <v>129962523</v>
       </c>
       <c r="B27" t="n">
         <v>98794</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560673</v>
+        <v>560660</v>
       </c>
       <c r="R27" t="n">
-        <v>6684885</v>
+        <v>6684913</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,7 +3630,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129962523</v>
+        <v>129962519</v>
       </c>
       <c r="B28" t="n">
         <v>98794</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560660</v>
+        <v>560673</v>
       </c>
       <c r="R28" t="n">
-        <v>6684913</v>
+        <v>6684885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3746,54 +3746,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129962516</v>
+        <v>129962499</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>96032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560566</v>
+        <v>560790</v>
       </c>
       <c r="R29" t="n">
-        <v>6684910</v>
+        <v>6685006</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3825,7 +3816,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3835,7 +3826,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3862,7 +3853,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962524</v>
+        <v>129962516</v>
       </c>
       <c r="B30" t="n">
         <v>98794</v>
@@ -3892,7 +3883,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3906,10 +3897,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560597</v>
+        <v>560566</v>
       </c>
       <c r="R30" t="n">
-        <v>6684810</v>
+        <v>6684910</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3941,7 +3932,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3951,7 +3942,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3978,59 +3969,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962513</v>
+        <v>129962502</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560545</v>
+        <v>560552</v>
       </c>
       <c r="R31" t="n">
-        <v>6684879</v>
+        <v>6684832</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4062,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4099,45 +4076,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129962499</v>
+        <v>129962513</v>
       </c>
       <c r="B32" t="n">
-        <v>96032</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560790</v>
+        <v>560545</v>
       </c>
       <c r="R32" t="n">
-        <v>6685006</v>
+        <v>6684879</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4169,7 +4160,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +4170,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,45 +4197,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962502</v>
+        <v>129962524</v>
       </c>
       <c r="B33" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560552</v>
+        <v>560597</v>
       </c>
       <c r="R33" t="n">
-        <v>6684832</v>
+        <v>6684810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -1470,45 +1470,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B9" t="n">
-        <v>92557</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R9" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,54 +1586,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>92557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R10" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2811,7 +2811,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129962509</v>
+        <v>129962515</v>
       </c>
       <c r="B21" t="n">
         <v>98794</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2849,21 +2849,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560768</v>
+        <v>560563</v>
       </c>
       <c r="R21" t="n">
-        <v>6685002</v>
+        <v>6684722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,7 +2890,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2900,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,7 +2927,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129962515</v>
+        <v>129962509</v>
       </c>
       <c r="B22" t="n">
         <v>98794</v>
@@ -2962,7 +2957,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2970,16 +2965,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560563</v>
+        <v>560768</v>
       </c>
       <c r="R22" t="n">
-        <v>6684722</v>
+        <v>6685002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3514,7 +3514,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129962523</v>
+        <v>129962519</v>
       </c>
       <c r="B27" t="n">
         <v>98794</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560660</v>
+        <v>560673</v>
       </c>
       <c r="R27" t="n">
-        <v>6684913</v>
+        <v>6684885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,7 +3630,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129962519</v>
+        <v>129962523</v>
       </c>
       <c r="B28" t="n">
         <v>98794</v>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560673</v>
+        <v>560660</v>
       </c>
       <c r="R28" t="n">
-        <v>6684885</v>
+        <v>6684913</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3969,45 +3969,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962502</v>
+        <v>129962524</v>
       </c>
       <c r="B31" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560552</v>
+        <v>560597</v>
       </c>
       <c r="R31" t="n">
-        <v>6684832</v>
+        <v>6684810</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,7 +4048,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4049,7 +4058,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4197,54 +4206,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962524</v>
+        <v>129962502</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560597</v>
+        <v>560552</v>
       </c>
       <c r="R33" t="n">
-        <v>6684810</v>
+        <v>6684832</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129962496</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129962526</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129962514</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>129962504</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>129962525</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129962491</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129962511</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>129962521</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129962492</v>
       </c>
       <c r="B10" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>129962506</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129962503</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129962501</v>
       </c>
       <c r="B13" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129962495</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>129962522</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129962507</v>
+        <v>129962493</v>
       </c>
       <c r="B19" t="n">
-        <v>58108</v>
+        <v>92560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560846</v>
+        <v>560790</v>
       </c>
       <c r="R19" t="n">
-        <v>6685065</v>
+        <v>6685002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129962493</v>
+        <v>129962507</v>
       </c>
       <c r="B20" t="n">
-        <v>92557</v>
+        <v>58111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560790</v>
+        <v>560846</v>
       </c>
       <c r="R20" t="n">
-        <v>6685002</v>
+        <v>6685065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2814,7 @@
         <v>129962515</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129962509</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129962517</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>129962518</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>129962494</v>
       </c>
       <c r="B25" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>129962505</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>129962519</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129962523</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129962499</v>
+        <v>129962502</v>
       </c>
       <c r="B29" t="n">
-        <v>96032</v>
+        <v>97668</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3757,21 +3757,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560790</v>
+        <v>560552</v>
       </c>
       <c r="R29" t="n">
-        <v>6685006</v>
+        <v>6684832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,54 +3853,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962516</v>
+        <v>129962499</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>96035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560566</v>
+        <v>560790</v>
       </c>
       <c r="R30" t="n">
-        <v>6684910</v>
+        <v>6685006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3923,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3933,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,10 +3960,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962524</v>
+        <v>129962516</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,7 +3990,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4013,10 +4004,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560597</v>
+        <v>560566</v>
       </c>
       <c r="R31" t="n">
-        <v>6684810</v>
+        <v>6684910</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4048,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,10 +4076,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129962513</v>
+        <v>129962524</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4115,7 +4106,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4123,21 +4114,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560545</v>
+        <v>560597</v>
       </c>
       <c r="R32" t="n">
-        <v>6684879</v>
+        <v>6684810</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4169,7 +4155,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +4165,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,45 +4192,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962502</v>
+        <v>129962513</v>
       </c>
       <c r="B33" t="n">
-        <v>97665</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560552</v>
+        <v>560545</v>
       </c>
       <c r="R33" t="n">
-        <v>6684832</v>
+        <v>6684879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129962493</v>
+        <v>129962507</v>
       </c>
       <c r="B19" t="n">
-        <v>92560</v>
+        <v>58111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560790</v>
+        <v>560846</v>
       </c>
       <c r="R19" t="n">
-        <v>6685002</v>
+        <v>6685065</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129962507</v>
+        <v>129962493</v>
       </c>
       <c r="B20" t="n">
-        <v>58111</v>
+        <v>92560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560846</v>
+        <v>560790</v>
       </c>
       <c r="R20" t="n">
-        <v>6685065</v>
+        <v>6685002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3290,38 +3290,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129962494</v>
+        <v>129962505</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560605</v>
+        <v>560597</v>
       </c>
       <c r="R25" t="n">
-        <v>6684821</v>
+        <v>6684753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,38 +3402,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129962505</v>
+        <v>129962494</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560597</v>
+        <v>560605</v>
       </c>
       <c r="R26" t="n">
-        <v>6684753</v>
+        <v>6684821</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129962526</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129962514</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>129962504</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>129962525</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129962491</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129962511</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,54 +1470,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>92561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R9" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,45 +1577,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B10" t="n">
-        <v>92560</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R10" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
         <v>129962506</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,50 +1805,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129962503</v>
+        <v>129962501</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>97669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560720</v>
+        <v>560587</v>
       </c>
       <c r="R12" t="n">
-        <v>6684848</v>
+        <v>6684762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,45 +1912,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962501</v>
+        <v>129962503</v>
       </c>
       <c r="B13" t="n">
-        <v>97668</v>
+        <v>98798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560587</v>
+        <v>560720</v>
       </c>
       <c r="R13" t="n">
-        <v>6684762</v>
+        <v>6684848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,38 +2024,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129962500</v>
+        <v>129962522</v>
       </c>
       <c r="B14" t="n">
-        <v>4773</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2064,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560603</v>
+        <v>560749</v>
       </c>
       <c r="R14" t="n">
-        <v>6684818</v>
+        <v>6685009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,47 +2257,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129962522</v>
+        <v>129962500</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>4773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560749</v>
+        <v>560603</v>
       </c>
       <c r="R16" t="n">
-        <v>6685009</v>
+        <v>6684818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,38 +2369,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962488</v>
+        <v>129962512</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2409,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560605</v>
+        <v>560755</v>
       </c>
       <c r="R17" t="n">
-        <v>6684821</v>
+        <v>6685020</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,42 +2485,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129962512</v>
+        <v>129962488</v>
       </c>
       <c r="B18" t="n">
-        <v>98797</v>
+        <v>5197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560755</v>
+        <v>560605</v>
       </c>
       <c r="R18" t="n">
-        <v>6685020</v>
+        <v>6684821</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129962507</v>
+        <v>129962493</v>
       </c>
       <c r="B19" t="n">
-        <v>58111</v>
+        <v>92561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560846</v>
+        <v>560790</v>
       </c>
       <c r="R19" t="n">
-        <v>6685065</v>
+        <v>6685002</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129962493</v>
+        <v>129962507</v>
       </c>
       <c r="B20" t="n">
-        <v>92560</v>
+        <v>58111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560790</v>
+        <v>560846</v>
       </c>
       <c r="R20" t="n">
-        <v>6685002</v>
+        <v>6685065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2814,7 @@
         <v>129962515</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129962509</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129962517</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>129962518</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,38 +3290,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129962505</v>
+        <v>129962494</v>
       </c>
       <c r="B25" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560597</v>
+        <v>560605</v>
       </c>
       <c r="R25" t="n">
-        <v>6684753</v>
+        <v>6684821</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,38 +3402,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129962494</v>
+        <v>129962505</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560605</v>
+        <v>560597</v>
       </c>
       <c r="R26" t="n">
-        <v>6684821</v>
+        <v>6684753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,7 +3517,7 @@
         <v>129962519</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129962523</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129962502</v>
+        <v>129962499</v>
       </c>
       <c r="B29" t="n">
-        <v>97668</v>
+        <v>96036</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3757,21 +3757,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>2813</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560552</v>
+        <v>560790</v>
       </c>
       <c r="R29" t="n">
-        <v>6684832</v>
+        <v>6685006</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,45 +3853,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962499</v>
+        <v>129962516</v>
       </c>
       <c r="B30" t="n">
-        <v>96035</v>
+        <v>98798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560790</v>
+        <v>560566</v>
       </c>
       <c r="R30" t="n">
-        <v>6685006</v>
+        <v>6684910</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3923,7 +3932,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3933,7 +3942,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,10 +3969,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962516</v>
+        <v>129962524</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3990,7 +3999,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4004,10 +4013,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560566</v>
+        <v>560597</v>
       </c>
       <c r="R31" t="n">
-        <v>6684910</v>
+        <v>6684810</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,7 +4048,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4049,7 +4058,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,10 +4085,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129962524</v>
+        <v>129962513</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,7 +4115,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4114,16 +4123,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560597</v>
+        <v>560545</v>
       </c>
       <c r="R32" t="n">
-        <v>6684810</v>
+        <v>6684879</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,7 +4169,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4165,7 +4179,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,59 +4206,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962513</v>
+        <v>129962502</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>97669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560545</v>
+        <v>560552</v>
       </c>
       <c r="R33" t="n">
-        <v>6684879</v>
+        <v>6684832</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129962496</v>
+        <v>129962526</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560548</v>
+        <v>560557</v>
       </c>
       <c r="R2" t="n">
-        <v>6684894</v>
+        <v>6684881</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,42 +791,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129962526</v>
+        <v>129962496</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560557</v>
+        <v>560548</v>
       </c>
       <c r="R3" t="n">
-        <v>6684881</v>
+        <v>6684894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1805,45 +1805,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129962501</v>
+        <v>129962503</v>
       </c>
       <c r="B12" t="n">
-        <v>97669</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560587</v>
+        <v>560720</v>
       </c>
       <c r="R12" t="n">
-        <v>6684762</v>
+        <v>6684848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,50 +1917,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962503</v>
+        <v>129962501</v>
       </c>
       <c r="B13" t="n">
-        <v>98798</v>
+        <v>97669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560720</v>
+        <v>560587</v>
       </c>
       <c r="R13" t="n">
-        <v>6684848</v>
+        <v>6684762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,47 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129962522</v>
+        <v>129962495</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2073,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560749</v>
+        <v>560546</v>
       </c>
       <c r="R14" t="n">
-        <v>6685009</v>
+        <v>6684846</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,38 +2136,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129962495</v>
+        <v>129962500</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>4773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2185,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560546</v>
+        <v>560603</v>
       </c>
       <c r="R15" t="n">
-        <v>6684846</v>
+        <v>6684818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,38 +2248,47 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129962500</v>
+        <v>129962522</v>
       </c>
       <c r="B16" t="n">
-        <v>4773</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560603</v>
+        <v>560749</v>
       </c>
       <c r="R16" t="n">
-        <v>6684818</v>
+        <v>6685009</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,42 +2369,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962512</v>
+        <v>129962488</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2413,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560755</v>
+        <v>560605</v>
       </c>
       <c r="R17" t="n">
-        <v>6685020</v>
+        <v>6684821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,38 +2481,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129962488</v>
+        <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>98798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560605</v>
+        <v>560755</v>
       </c>
       <c r="R18" t="n">
-        <v>6684821</v>
+        <v>6685020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3290,38 +3290,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129962494</v>
+        <v>129962505</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>98798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560605</v>
+        <v>560597</v>
       </c>
       <c r="R25" t="n">
-        <v>6684821</v>
+        <v>6684753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,38 +3402,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129962505</v>
+        <v>129962494</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560597</v>
+        <v>560605</v>
       </c>
       <c r="R26" t="n">
-        <v>6684753</v>
+        <v>6684821</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129962526</v>
+        <v>129962496</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560557</v>
+        <v>560548</v>
       </c>
       <c r="R2" t="n">
-        <v>6684881</v>
+        <v>6684894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129962496</v>
+        <v>129962526</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560548</v>
+        <v>560557</v>
       </c>
       <c r="R3" t="n">
-        <v>6684894</v>
+        <v>6684881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +906,7 @@
         <v>129962514</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>129962504</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>129962525</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129962491</v>
       </c>
       <c r="B7" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129962511</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,45 +1470,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B9" t="n">
-        <v>92561</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R9" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,54 +1586,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>92578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R10" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
         <v>129962506</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,50 +1805,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129962503</v>
+        <v>129962501</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>97686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560720</v>
+        <v>560587</v>
       </c>
       <c r="R12" t="n">
-        <v>6684848</v>
+        <v>6684762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,45 +1912,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962501</v>
+        <v>129962503</v>
       </c>
       <c r="B13" t="n">
-        <v>97669</v>
+        <v>98815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560587</v>
+        <v>560720</v>
       </c>
       <c r="R13" t="n">
-        <v>6684762</v>
+        <v>6684848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,38 +2136,47 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129962500</v>
+        <v>129962522</v>
       </c>
       <c r="B15" t="n">
-        <v>4773</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2176,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560603</v>
+        <v>560749</v>
       </c>
       <c r="R15" t="n">
-        <v>6684818</v>
+        <v>6685009</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,47 +2257,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129962522</v>
+        <v>129962500</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>4773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560749</v>
+        <v>560603</v>
       </c>
       <c r="R16" t="n">
-        <v>6685009</v>
+        <v>6684818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,7 +2484,7 @@
         <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129962493</v>
       </c>
       <c r="B19" t="n">
-        <v>92561</v>
+        <v>92578</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>129962507</v>
       </c>
       <c r="B20" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129962515</v>
+        <v>129962517</v>
       </c>
       <c r="B21" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2849,16 +2849,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560563</v>
+        <v>560660</v>
       </c>
       <c r="R21" t="n">
-        <v>6684722</v>
+        <v>6684910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2900,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129962509</v>
+        <v>129962518</v>
       </c>
       <c r="B22" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560768</v>
+        <v>560591</v>
       </c>
       <c r="R22" t="n">
-        <v>6685002</v>
+        <v>6684793</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,10 +3053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129962517</v>
+        <v>129962509</v>
       </c>
       <c r="B23" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3083,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3097,10 +3102,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560660</v>
+        <v>560768</v>
       </c>
       <c r="R23" t="n">
-        <v>6684910</v>
+        <v>6685002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3132,7 +3137,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +3147,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,10 +3174,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129962518</v>
+        <v>129962515</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3199,7 +3204,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3207,21 +3212,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560591</v>
+        <v>560563</v>
       </c>
       <c r="R24" t="n">
-        <v>6684793</v>
+        <v>6684722</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,7 +3293,7 @@
         <v>129962505</v>
       </c>
       <c r="B25" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129962519</v>
+        <v>129962523</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560673</v>
+        <v>560660</v>
       </c>
       <c r="R27" t="n">
-        <v>6684885</v>
+        <v>6684913</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,10 +3630,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129962523</v>
+        <v>129962519</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560660</v>
+        <v>560673</v>
       </c>
       <c r="R28" t="n">
-        <v>6684913</v>
+        <v>6684885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,7 +3749,7 @@
         <v>129962499</v>
       </c>
       <c r="B29" t="n">
-        <v>96036</v>
+        <v>96053</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3853,54 +3853,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962516</v>
+        <v>129962502</v>
       </c>
       <c r="B30" t="n">
-        <v>98798</v>
+        <v>97686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560566</v>
+        <v>560552</v>
       </c>
       <c r="R30" t="n">
-        <v>6684910</v>
+        <v>6684832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3923,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3933,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,10 +3960,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962524</v>
+        <v>129962516</v>
       </c>
       <c r="B31" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,7 +3990,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4013,10 +4004,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560597</v>
+        <v>560566</v>
       </c>
       <c r="R31" t="n">
-        <v>6684810</v>
+        <v>6684910</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4048,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,7 +4079,7 @@
         <v>129962513</v>
       </c>
       <c r="B32" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4206,45 +4197,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962502</v>
+        <v>129962524</v>
       </c>
       <c r="B33" t="n">
-        <v>97669</v>
+        <v>98815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560552</v>
+        <v>560597</v>
       </c>
       <c r="R33" t="n">
-        <v>6684832</v>
+        <v>6684810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -1470,45 +1470,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B9" t="n">
-        <v>92594</v>
+        <v>98831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R9" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,54 +1586,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>92594</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R10" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2024,38 +2024,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129962500</v>
+        <v>129962495</v>
       </c>
       <c r="B14" t="n">
-        <v>4773</v>
+        <v>57738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560603</v>
+        <v>560546</v>
       </c>
       <c r="R14" t="n">
-        <v>6684818</v>
+        <v>6684846</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,38 +2136,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129962495</v>
+        <v>129962500</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>4773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560546</v>
+        <v>560603</v>
       </c>
       <c r="R15" t="n">
-        <v>6684846</v>
+        <v>6684818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,42 +2369,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962512</v>
+        <v>129962488</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2413,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560755</v>
+        <v>560605</v>
       </c>
       <c r="R17" t="n">
-        <v>6685020</v>
+        <v>6684821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,38 +2481,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129962488</v>
+        <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>98831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560605</v>
+        <v>560755</v>
       </c>
       <c r="R18" t="n">
-        <v>6684821</v>
+        <v>6685020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3746,10 +3746,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129962499</v>
+        <v>129962502</v>
       </c>
       <c r="B29" t="n">
-        <v>96069</v>
+        <v>97702</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3757,21 +3757,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2813</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560790</v>
+        <v>560552</v>
       </c>
       <c r="R29" t="n">
-        <v>6685006</v>
+        <v>6684832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,54 +3853,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962516</v>
+        <v>129962499</v>
       </c>
       <c r="B30" t="n">
-        <v>98831</v>
+        <v>96069</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560566</v>
+        <v>560790</v>
       </c>
       <c r="R30" t="n">
-        <v>6684910</v>
+        <v>6685006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3923,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3933,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,7 +3960,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962524</v>
+        <v>129962516</v>
       </c>
       <c r="B31" t="n">
         <v>98831</v>
@@ -3999,7 +3990,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4013,10 +4004,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560597</v>
+        <v>560566</v>
       </c>
       <c r="R31" t="n">
-        <v>6684810</v>
+        <v>6684910</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4048,7 +4039,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +4049,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,7 +4076,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129962513</v>
+        <v>129962524</v>
       </c>
       <c r="B32" t="n">
         <v>98831</v>
@@ -4115,7 +4106,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4123,21 +4114,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560545</v>
+        <v>560597</v>
       </c>
       <c r="R32" t="n">
-        <v>6684879</v>
+        <v>6684810</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4169,7 +4155,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +4165,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,45 +4192,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962502</v>
+        <v>129962513</v>
       </c>
       <c r="B33" t="n">
-        <v>97702</v>
+        <v>98831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560552</v>
+        <v>560545</v>
       </c>
       <c r="R33" t="n">
-        <v>6684832</v>
+        <v>6684879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -1470,54 +1470,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>92594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R9" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,45 +1577,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B10" t="n">
-        <v>92594</v>
+        <v>98831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R10" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129962496</v>
+        <v>129962526</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560548</v>
+        <v>560557</v>
       </c>
       <c r="R2" t="n">
-        <v>6684894</v>
+        <v>6684881</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,42 +791,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129962526</v>
+        <v>129962496</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560557</v>
+        <v>560548</v>
       </c>
       <c r="R3" t="n">
-        <v>6684881</v>
+        <v>6684894</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +906,7 @@
         <v>129962514</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>129962504</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>129962525</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129962491</v>
       </c>
       <c r="B7" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129962511</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,45 +1470,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962492</v>
+        <v>129962521</v>
       </c>
       <c r="B9" t="n">
-        <v>92594</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560800</v>
+        <v>560923</v>
       </c>
       <c r="R9" t="n">
-        <v>6684995</v>
+        <v>6685070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,54 +1586,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962521</v>
+        <v>129962492</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>92596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560923</v>
+        <v>560800</v>
       </c>
       <c r="R10" t="n">
-        <v>6685070</v>
+        <v>6684995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1696,7 @@
         <v>129962506</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,45 +1805,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129962501</v>
+        <v>129962503</v>
       </c>
       <c r="B12" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560587</v>
+        <v>560720</v>
       </c>
       <c r="R12" t="n">
-        <v>6684762</v>
+        <v>6684848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,50 +1917,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962503</v>
+        <v>129962501</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560720</v>
+        <v>560587</v>
       </c>
       <c r="R13" t="n">
-        <v>6684848</v>
+        <v>6684762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2251,7 +2251,7 @@
         <v>129962522</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>129962493</v>
       </c>
       <c r="B19" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>129962515</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129962509</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129962517</v>
       </c>
       <c r="B23" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>129962518</v>
       </c>
       <c r="B24" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,38 +3290,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129962505</v>
+        <v>129962494</v>
       </c>
       <c r="B25" t="n">
-        <v>98831</v>
+        <v>57738</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560597</v>
+        <v>560605</v>
       </c>
       <c r="R25" t="n">
-        <v>6684753</v>
+        <v>6684821</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,38 +3402,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129962494</v>
+        <v>129962505</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>98833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560605</v>
+        <v>560597</v>
       </c>
       <c r="R26" t="n">
-        <v>6684821</v>
+        <v>6684753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,7 +3517,7 @@
         <v>129962519</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129962523</v>
       </c>
       <c r="B28" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,45 +3746,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129962502</v>
+        <v>129962516</v>
       </c>
       <c r="B29" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560552</v>
+        <v>560566</v>
       </c>
       <c r="R29" t="n">
-        <v>6684832</v>
+        <v>6684910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,7 +3825,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3826,7 +3835,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,45 +3862,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962499</v>
+        <v>129962524</v>
       </c>
       <c r="B30" t="n">
-        <v>96069</v>
+        <v>98833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560790</v>
+        <v>560597</v>
       </c>
       <c r="R30" t="n">
-        <v>6685006</v>
+        <v>6684810</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3923,7 +3941,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3933,7 +3951,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,10 +3978,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962516</v>
+        <v>129962513</v>
       </c>
       <c r="B31" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3998,16 +4016,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560566</v>
+        <v>560545</v>
       </c>
       <c r="R31" t="n">
-        <v>6684910</v>
+        <v>6684879</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4049,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,54 +4099,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129962524</v>
+        <v>129962499</v>
       </c>
       <c r="B32" t="n">
-        <v>98831</v>
+        <v>96071</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560597</v>
+        <v>560790</v>
       </c>
       <c r="R32" t="n">
-        <v>6684810</v>
+        <v>6685006</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,7 +4169,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4165,7 +4179,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,59 +4206,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129962513</v>
+        <v>129962502</v>
       </c>
       <c r="B33" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560545</v>
+        <v>560552</v>
       </c>
       <c r="R33" t="n">
-        <v>6684879</v>
+        <v>6684832</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129962526</v>
+        <v>129962496</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560557</v>
+        <v>560548</v>
       </c>
       <c r="R2" t="n">
-        <v>6684881</v>
+        <v>6684894</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,38 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129962496</v>
+        <v>129962526</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560548</v>
+        <v>560557</v>
       </c>
       <c r="R3" t="n">
-        <v>6684894</v>
+        <v>6684881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +906,7 @@
         <v>129962514</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>129962504</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>129962525</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129962491</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129962511</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>129962521</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129962492</v>
       </c>
       <c r="B10" t="n">
-        <v>92596</v>
+        <v>92683</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>129962506</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,50 +1805,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129962503</v>
+        <v>129962501</v>
       </c>
       <c r="B12" t="n">
-        <v>98833</v>
+        <v>97791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560720</v>
+        <v>560587</v>
       </c>
       <c r="R12" t="n">
-        <v>6684848</v>
+        <v>6684762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,45 +1912,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962501</v>
+        <v>129962503</v>
       </c>
       <c r="B13" t="n">
-        <v>97704</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560587</v>
+        <v>560720</v>
       </c>
       <c r="R13" t="n">
-        <v>6684762</v>
+        <v>6684848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,38 +2024,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129962495</v>
+        <v>129962522</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2064,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560546</v>
+        <v>560749</v>
       </c>
       <c r="R14" t="n">
-        <v>6684846</v>
+        <v>6685009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,38 +2145,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129962500</v>
+        <v>129962495</v>
       </c>
       <c r="B15" t="n">
-        <v>4773</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2176,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560603</v>
+        <v>560546</v>
       </c>
       <c r="R15" t="n">
-        <v>6684818</v>
+        <v>6684846</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,47 +2257,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129962522</v>
+        <v>129962500</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>4773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560749</v>
+        <v>560603</v>
       </c>
       <c r="R16" t="n">
-        <v>6685009</v>
+        <v>6684818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,38 +2369,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962488</v>
+        <v>129962512</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2409,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560605</v>
+        <v>560755</v>
       </c>
       <c r="R17" t="n">
-        <v>6684821</v>
+        <v>6685020</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,42 +2485,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129962512</v>
+        <v>129962488</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>5197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560755</v>
+        <v>560605</v>
       </c>
       <c r="R18" t="n">
-        <v>6685020</v>
+        <v>6684821</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,10 +2597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129962493</v>
+        <v>129962507</v>
       </c>
       <c r="B19" t="n">
-        <v>92596</v>
+        <v>58198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560790</v>
+        <v>560846</v>
       </c>
       <c r="R19" t="n">
-        <v>6685002</v>
+        <v>6685065</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129962507</v>
+        <v>129962493</v>
       </c>
       <c r="B20" t="n">
-        <v>58113</v>
+        <v>92683</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560846</v>
+        <v>560790</v>
       </c>
       <c r="R20" t="n">
-        <v>6685065</v>
+        <v>6685002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,10 +2811,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129962515</v>
+        <v>129962509</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2849,16 +2849,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560563</v>
+        <v>560768</v>
       </c>
       <c r="R21" t="n">
-        <v>6684722</v>
+        <v>6685002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2900,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129962509</v>
+        <v>129962518</v>
       </c>
       <c r="B22" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2957,7 +2962,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560768</v>
+        <v>560591</v>
       </c>
       <c r="R22" t="n">
-        <v>6685002</v>
+        <v>6684793</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,10 +3053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129962517</v>
+        <v>129962515</v>
       </c>
       <c r="B23" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3083,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3086,21 +3091,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560660</v>
+        <v>560563</v>
       </c>
       <c r="R23" t="n">
-        <v>6684910</v>
+        <v>6684722</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129962518</v>
+        <v>129962517</v>
       </c>
       <c r="B24" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560591</v>
+        <v>560660</v>
       </c>
       <c r="R24" t="n">
-        <v>6684793</v>
+        <v>6684910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,7 +3293,7 @@
         <v>129962494</v>
       </c>
       <c r="B25" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>129962505</v>
       </c>
       <c r="B26" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>129962519</v>
       </c>
       <c r="B27" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>129962523</v>
       </c>
       <c r="B28" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>129962516</v>
       </c>
       <c r="B29" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>129962524</v>
       </c>
       <c r="B30" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>129962513</v>
       </c>
       <c r="B31" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>129962499</v>
       </c>
       <c r="B32" t="n">
-        <v>96071</v>
+        <v>96158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129962502</v>
       </c>
       <c r="B33" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129962496</v>
+        <v>129962491</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560548</v>
+        <v>560573</v>
       </c>
       <c r="R2" t="n">
-        <v>6684894</v>
+        <v>6684851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129962526</v>
+        <v>129962499</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560557</v>
+        <v>560790</v>
       </c>
       <c r="R3" t="n">
-        <v>6684881</v>
+        <v>6685006</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129962514</v>
+        <v>129962492</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560663</v>
+        <v>560800</v>
       </c>
       <c r="R4" t="n">
-        <v>6684926</v>
+        <v>6684995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129962504</v>
+        <v>129962493</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560751</v>
+        <v>560790</v>
       </c>
       <c r="R5" t="n">
-        <v>6684862</v>
+        <v>6685002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,42 +1103,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129962525</v>
+        <v>129962494</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560541</v>
+        <v>560605</v>
       </c>
       <c r="R6" t="n">
-        <v>6684880</v>
+        <v>6684821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,45 +1215,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129962491</v>
+        <v>129962495</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560573</v>
+        <v>560546</v>
       </c>
       <c r="R7" t="n">
-        <v>6684851</v>
+        <v>6684846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,42 +1327,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129962511</v>
+        <v>129962496</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1398,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560605</v>
+        <v>560548</v>
       </c>
       <c r="R8" t="n">
-        <v>6684827</v>
+        <v>6684894</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129962492</v>
+        <v>129962500</v>
       </c>
       <c r="B9" t="n">
-        <v>92683</v>
+        <v>4775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,34 +1450,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560800</v>
+        <v>560603</v>
       </c>
       <c r="R9" t="n">
-        <v>6684995</v>
+        <v>6684818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,54 +1551,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129962521</v>
+        <v>129962507</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560923</v>
+        <v>560846</v>
       </c>
       <c r="R10" t="n">
-        <v>6685070</v>
+        <v>6685065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,38 +1658,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129962506</v>
+        <v>129962488</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>5199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1733,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560575</v>
+        <v>560605</v>
       </c>
       <c r="R11" t="n">
-        <v>6684860</v>
+        <v>6684821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,7 +1773,7 @@
         <v>129962503</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,45 +1882,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129962501</v>
+        <v>129962504</v>
       </c>
       <c r="B13" t="n">
-        <v>97791</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560587</v>
+        <v>560751</v>
       </c>
       <c r="R13" t="n">
-        <v>6684762</v>
+        <v>6684862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,38 +1994,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129962500</v>
+        <v>129962505</v>
       </c>
       <c r="B14" t="n">
-        <v>4773</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2064,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560603</v>
+        <v>560597</v>
       </c>
       <c r="R14" t="n">
-        <v>6684818</v>
+        <v>6684753</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2079,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129962522</v>
+        <v>129962506</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,16 +2134,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2185,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560749</v>
+        <v>560575</v>
       </c>
       <c r="R15" t="n">
-        <v>6685009</v>
+        <v>6684860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,38 +2218,47 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129962495</v>
+        <v>129962509</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2297,10 +2267,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560546</v>
+        <v>560768</v>
       </c>
       <c r="R16" t="n">
-        <v>6684846</v>
+        <v>6685002</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2312,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129962512</v>
+        <v>129962511</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560755</v>
+        <v>560605</v>
       </c>
       <c r="R17" t="n">
-        <v>6685020</v>
+        <v>6684827</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,38 +2455,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129962488</v>
+        <v>129962512</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2525,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560605</v>
+        <v>560755</v>
       </c>
       <c r="R18" t="n">
-        <v>6684821</v>
+        <v>6685020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,45 +2571,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129962493</v>
+        <v>129962513</v>
       </c>
       <c r="B19" t="n">
-        <v>92683</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560790</v>
+        <v>560545</v>
       </c>
       <c r="R19" t="n">
-        <v>6685002</v>
+        <v>6684879</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,45 +2692,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129962507</v>
+        <v>129962514</v>
       </c>
       <c r="B20" t="n">
-        <v>58198</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560846</v>
+        <v>560663</v>
       </c>
       <c r="R20" t="n">
-        <v>6685065</v>
+        <v>6684926</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2811,7 @@
         <v>129962515</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129962509</v>
+        <v>129962516</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2957,7 +2954,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2965,21 +2962,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560768</v>
+        <v>560566</v>
       </c>
       <c r="R22" t="n">
-        <v>6685002</v>
+        <v>6684910</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,7 +3043,7 @@
         <v>129962517</v>
       </c>
       <c r="B23" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,7 +3164,7 @@
         <v>129962518</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,10 +3282,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129962505</v>
+        <v>129962519</v>
       </c>
       <c r="B25" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,10 +3310,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,10 +3326,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560597</v>
+        <v>560673</v>
       </c>
       <c r="R25" t="n">
-        <v>6684753</v>
+        <v>6684885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3365,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,38 +3398,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129962494</v>
+        <v>129962521</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560605</v>
+        <v>560923</v>
       </c>
       <c r="R26" t="n">
-        <v>6684821</v>
+        <v>6685070</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129962519</v>
+        <v>129962522</v>
       </c>
       <c r="B27" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3552,16 +3552,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560673</v>
+        <v>560749</v>
       </c>
       <c r="R27" t="n">
-        <v>6684885</v>
+        <v>6685009</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,7 +3598,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3603,7 +3608,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3633,7 +3638,7 @@
         <v>129962523</v>
       </c>
       <c r="B28" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3746,45 +3751,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129962499</v>
+        <v>129962524</v>
       </c>
       <c r="B29" t="n">
-        <v>96158</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560790</v>
+        <v>560597</v>
       </c>
       <c r="R29" t="n">
-        <v>6685006</v>
+        <v>6684810</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3816,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3826,7 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,10 +3867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129962516</v>
+        <v>129962525</v>
       </c>
       <c r="B30" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3883,7 +3897,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3897,10 +3911,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560566</v>
+        <v>560541</v>
       </c>
       <c r="R30" t="n">
-        <v>6684910</v>
+        <v>6684880</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,7 +3946,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3942,7 +3956,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3969,10 +3983,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129962524</v>
+        <v>129962526</v>
       </c>
       <c r="B31" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,10 +4027,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560597</v>
+        <v>560557</v>
       </c>
       <c r="R31" t="n">
-        <v>6684810</v>
+        <v>6684881</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4048,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4058,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,59 +4099,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129962513</v>
+        <v>129962501</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>97983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörboberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560545</v>
+        <v>560587</v>
       </c>
       <c r="R32" t="n">
-        <v>6684879</v>
+        <v>6684762</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,7 +4209,7 @@
         <v>129962502</v>
       </c>
       <c r="B33" t="n">
-        <v>97791</v>
+        <v>97983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 53820-2025 artfynd.xlsx
+++ b/artfynd/A 53820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962491</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962499</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962492</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962493</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962494</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962495</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962496</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962507</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962488</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962503</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962504</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2103,6 +2168,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962505</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962506</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2336,6 +2411,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962509</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962511</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2568,6 +2653,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962512</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2689,6 +2779,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962513</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2805,6 +2900,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962514</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2921,6 +3021,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962515</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3037,6 +3142,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962516</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3158,6 +3268,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962517</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3279,6 +3394,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962518</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3395,6 +3515,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962519</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3511,6 +3636,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962521</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3632,6 +3762,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962522</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3748,6 +3883,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962523</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3864,6 +4004,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962524</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3980,6 +4125,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962525</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4096,6 +4246,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962526</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4203,6 +4358,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962501</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4310,8 +4470,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962502</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>